--- a/pipeline/credit_rating/output/visrating_xhtn_20261030.xlsx
+++ b/pipeline/credit_rating/output/visrating_xhtn_20261030.xlsx
@@ -581,7 +581,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q2" s="1" t="n">
@@ -662,7 +662,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q3" s="1" t="n">
@@ -739,7 +739,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q4" s="1" t="n">
@@ -812,7 +812,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q5" s="1" t="n">
@@ -885,7 +885,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q6" s="1" t="n">
@@ -962,7 +962,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q7" s="1" t="n">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q8" s="1" t="n">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q9" s="1" t="n">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q10" s="1" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q11" s="1" t="n">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q12" s="1" t="n">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q13" s="1" t="n">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q14" s="1" t="n">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q15" s="1" t="n">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q16" s="1" t="n">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q17" s="1" t="n">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q18" s="1" t="n">
@@ -1870,7 +1870,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q19" s="1" t="n">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q20" s="1" t="n">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q21" s="1" t="n">
@@ -2109,7 +2109,7 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q22" s="1" t="n">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q23" s="1" t="n">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q24" s="1" t="n">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q25" s="1" t="n">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q26" s="1" t="n">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q27" s="1" t="n">
@@ -2567,7 +2567,7 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q28" s="1" t="n">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q29" s="1" t="n">
@@ -2713,7 +2713,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q30" s="1" t="n">
@@ -2782,7 +2782,7 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q31" s="1" t="n">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q32" s="1" t="n">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q33" s="1" t="n">
@@ -3009,7 +3009,7 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q34" s="1" t="n">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q35" s="1" t="n">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q36" s="1" t="n">
@@ -3228,7 +3228,7 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q37" s="1" t="n">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q38" s="1" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q39" s="1" t="n">
@@ -3435,7 +3435,7 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q40" s="1" t="n">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q41" s="1" t="n">
@@ -3589,7 +3589,7 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q42" s="1" t="n">
@@ -3658,7 +3658,7 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q43" s="1" t="n">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q44" s="1" t="n">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q45" s="1" t="n">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q46" s="1" t="n">
@@ -3966,7 +3966,7 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q47" s="1" t="n">
@@ -4043,7 +4043,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q48" s="1" t="n">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q49" s="1" t="n">
@@ -4193,7 +4193,7 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q50" s="1" t="n">
@@ -4262,7 +4262,7 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q51" s="1" t="n">
@@ -4335,7 +4335,7 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q52" s="1" t="n">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q53" s="1" t="n">
@@ -4489,7 +4489,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q54" s="1" t="n">
@@ -4558,7 +4558,7 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q55" s="1" t="n">
@@ -4627,7 +4627,7 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q56" s="1" t="n">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q57" s="1" t="n">
@@ -4773,7 +4773,7 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q58" s="1" t="n">
@@ -4850,7 +4850,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q59" s="1" t="n">
@@ -4919,7 +4919,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q60" s="1" t="n">
@@ -4988,7 +4988,7 @@
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q61" s="1" t="n">
@@ -5057,7 +5057,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q62" s="1" t="n">
@@ -5134,7 +5134,7 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q63" s="1" t="n">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q64" s="1" t="n">
@@ -5280,7 +5280,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q65" s="1" t="n">
@@ -5357,7 +5357,7 @@
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q66" s="1" t="n">
@@ -5426,7 +5426,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q67" s="1" t="n">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q68" s="1" t="n">
@@ -5584,7 +5584,7 @@
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q69" s="1" t="n">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q70" s="1" t="n">
@@ -5738,7 +5738,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q71" s="1" t="n">
@@ -5815,7 +5815,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q72" s="1" t="n">
@@ -5892,7 +5892,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q73" s="1" t="n">
@@ -5965,7 +5965,7 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q74" s="1" t="n">
@@ -6038,7 +6038,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q75" s="1" t="n">
@@ -6107,7 +6107,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q76" s="1" t="n">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q77" s="1" t="n">
@@ -6257,7 +6257,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q78" s="1" t="n">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q79" s="1" t="n">
@@ -6403,7 +6403,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q80" s="1" t="n">
@@ -6480,7 +6480,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q81" s="1" t="n">
@@ -6549,7 +6549,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q82" s="1" t="n">
@@ -6618,7 +6618,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q83" s="1" t="n">
@@ -6687,7 +6687,7 @@
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q84" s="1" t="n">
@@ -6756,7 +6756,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q85" s="1" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q86" s="1" t="n">
@@ -6894,7 +6894,7 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q87" s="1" t="n">
@@ -6963,7 +6963,7 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q88" s="1" t="n">
@@ -7040,7 +7040,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q89" s="1" t="n">
@@ -7109,7 +7109,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q90" s="1" t="n">
@@ -7186,7 +7186,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q91" s="1" t="n">
@@ -7263,7 +7263,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q92" s="1" t="n">
@@ -7340,7 +7340,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q93" s="1" t="n">
@@ -7417,7 +7417,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q94" s="1" t="n">
@@ -7494,7 +7494,7 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q95" s="1" t="n">
@@ -7571,7 +7571,7 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q96" s="1" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q97" s="1" t="n">
@@ -7725,7 +7725,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q98" s="1" t="n">
@@ -7806,7 +7806,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q99" s="1" t="n">
@@ -7887,7 +7887,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q100" s="1" t="n">
@@ -7968,7 +7968,7 @@
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q101" s="1" t="n">
@@ -8045,7 +8045,7 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q102" s="1" t="n">
@@ -8114,7 +8114,7 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q103" s="1" t="n">
@@ -8187,7 +8187,7 @@
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q104" s="1" t="n">
@@ -8264,7 +8264,7 @@
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q105" s="1" t="n">
@@ -8341,7 +8341,7 @@
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q106" s="1" t="n">
@@ -8418,7 +8418,7 @@
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q107" s="1" t="n">
@@ -8495,7 +8495,7 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q108" s="1" t="n">
@@ -8572,7 +8572,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q109" s="1" t="n">
@@ -8649,7 +8649,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q110" s="1" t="n">
@@ -8718,7 +8718,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q111" s="1" t="n">
@@ -8795,7 +8795,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q112" s="1" t="n">
@@ -8864,7 +8864,7 @@
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q113" s="1" t="n">
@@ -8933,7 +8933,7 @@
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q114" s="1" t="n">
@@ -9010,7 +9010,7 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q115" s="1" t="n">
@@ -9079,7 +9079,7 @@
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q116" s="1" t="n">
@@ -9148,7 +9148,7 @@
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q117" s="1" t="n">
@@ -9217,7 +9217,7 @@
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q118" s="1" t="n">
@@ -9286,7 +9286,7 @@
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q119" s="1" t="n">
@@ -9363,7 +9363,7 @@
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q120" s="1" t="n">
@@ -9440,7 +9440,7 @@
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q121" s="1" t="n">
@@ -9517,7 +9517,7 @@
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q122" s="1" t="n">
@@ -9594,7 +9594,7 @@
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q123" s="1" t="n">
@@ -9671,7 +9671,7 @@
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q124" s="1" t="n">
@@ -9748,7 +9748,7 @@
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q125" s="1" t="n">
@@ -9825,7 +9825,7 @@
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>2026-10-30 10:23:46</t>
+          <t>2026-10-30 15:13:36</t>
         </is>
       </c>
       <c r="Q126" s="1" t="n">
